--- a/android/app/src/main/assets/public/files/CHR/ev_join.xlsx
+++ b/android/app/src/main/assets/public/files/CHR/ev_join.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\CHR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77CA6F9-72F1-4109-9808-74FD58D91918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B68DA1-2F01-42EF-8599-4A19C7390026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="225" windowWidth="26205" windowHeight="14850" xr2:uid="{C0E8C2FE-F33F-4C68-94BE-01501C7913C0}"/>
+    <workbookView xWindow="2025" yWindow="555" windowWidth="26205" windowHeight="14850" xr2:uid="{C0E8C2FE-F33F-4C68-94BE-01501C7913C0}"/>
   </bookViews>
   <sheets>
     <sheet name="4ノア" sheetId="9" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="355">
   <si>
     <t>愚者</t>
     <rPh sb="0" eb="2">
@@ -1612,90 +1612,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>視線はずっと前から感じていた。 瓦礫の陰、崩れた柱の裏。一定の距離を保ちながら、何者かが私を執拗に観察している気配。 敵意はない。だが、ひどく怯えたような、迷うような視線だった。</t>
-  </si>
-  <si>
-    <t>私が銃を下ろし、あえて隙を見せて待っていると、やがて瓦礫の隙間からおずおずと小さな影が姿を現した。</t>
-  </si>
-  <si>
-    <t>「お、おい……そこの、お前」</t>
-  </si>
-  <si>
-    <t>声は微かに震えていた。 現れたのは、ひどく小柄で華奢な少女だった。 だが、その可憐な外見に反して、言葉遣いはやけに尊大で男性的だ。</t>
-  </si>
-  <si>
-    <t>虚勢を張って胸を反らせているが、華奢な肩は小刻みに震え、大きな瞳は不安げに揺らいでいる。 本来はプライドが高い性質なのだろう。だが、この絶望的な世界でたった一人、孤独と恐怖に耐え続けて限界を迎えているのは明白だった。</t>
-  </si>
-  <si>
-    <t>私はゆっくりと銃を地面に置き、両手を広げて一切の敵意がないことを示した。</t>
-  </si>
-  <si>
-    <t>私が極力声を落とし、ゆっくりと歩み寄ると、ノアはビクッと体をこわばらせた。 だが、逃げ出そうとはしなかった。 足元まで近づき、その小さな頭にそっと手を乗せる。</t>
-  </si>
-  <si>
-    <t>強張っていたノアの顔が、くしゃりと歪んだ。</t>
-  </si>
-  <si>
-    <t>「ぼ、ボクは……別に、怖くなんか……っ、うぅ……っ」 尊大な態度はとうに崩れ去っていた。 ノアは私の服の裾をぎゅっと強く握りしめ、小さな子供のように嗚咽を漏らし始めた。</t>
-  </si>
-  <si>
-    <t>私はその背中を、落ち着くまでただ優しく撫で続けた。 彼女がどれほどの時間を、この暗闇の中で一人震えて過ごしてきたのか、痛いほど分かったからだ。</t>
-  </si>
-  <si>
-    <t>ノアはまだ赤い目をこすりながら、こくりと小さく頷いた。 こうして、過酷なタワーの探索に、小さくて少し生意気な同行者が加わることになった。</t>
-  </si>
-  <si>
-    <t>「ボクの名はノア。……その、ずっと見ていたんだが、お前、なかなかやるじゃないか。ボ、ボクが特別に声をかけてやったんだ、光栄に思えよ」</t>
-    <rPh sb="4" eb="5">
-      <t>ナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「えっ……」 「怖かったでしょう。偉かったね。もう大丈夫だよ」</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「ノア、私は紫苑」 やがて泣き止み、バツが悪そうに俯く彼女に、私はしゃがみ込んで目線を合わせ、穏やかに微笑みかけた。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「……お、お前が、どうしてもボクの力が必要だって言うなら……同行してやらないこともないぞ」</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">「私は今、人探しをしているんだ。……もし君さえよければ、私と一緒に来ない？」 </t>
-    <rPh sb="5" eb="7">
-      <t>ヒトサガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「うん、必要だ。一人でも多ければ心強いよ。」</t>
-    <rPh sb="4" eb="6">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ココロヅヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">「……ノア、だね」 </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「ひっ……な、なんだ。ボクに近づく気か！？」</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「大丈夫だ、取って食ったりしない。よく一人でここまで生き延びてきたね」</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <r>
       <t>[画像：evp008</t>
     </r>
@@ -1720,6 +1636,115 @@
       </rPr>
       <t xml:space="preserve"> ／ BGM：JOIN_US.mp3]</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>返事はない。ただ、気配がさらに強張るのが分かった。</t>
+  </si>
+  <si>
+    <t>紫苑「大丈夫です。危害を加えたりしません」</t>
+  </si>
+  <si>
+    <t>紫苑は両手を広げた。</t>
+  </si>
+  <si>
+    <t>やがて瓦礫の陰から、大きな本を抱えた小さな人影が、警戒しながら姿を見せる。</t>
+  </si>
+  <si>
+    <t>——それを目にした瞬間、紫苑の声から硬さが抜けた。</t>
+  </si>
+  <si>
+    <t>紫苑「……名前、聞いてもいい?」</t>
+  </si>
+  <si>
+    <t>ノア「……ボクはノア」</t>
+  </si>
+  <si>
+    <t>紫苑「私は紫苑」</t>
+  </si>
+  <si>
+    <t>ノア「わけの分からないところに迷い込んで、連れとはぐれた。……何か知らないか」</t>
+  </si>
+  <si>
+    <t>紫苑「ごめん、私にも分からない」</t>
+  </si>
+  <si>
+    <t>ノア「……そうか」</t>
+  </si>
+  <si>
+    <t>その時、遠くで瓦礫が崩れる音がした。ノアの肩が大きく跳ねる。</t>
+  </si>
+  <si>
+    <t>ノア「……っ、今のは」</t>
+  </si>
+  <si>
+    <t>紫苑「たぶん、何かが崩れただけだよ」</t>
+  </si>
+  <si>
+    <t>ノア「どこかでまた化け物が…」</t>
+  </si>
+  <si>
+    <t>そう言う手は、本を強く握りしめていた。</t>
+  </si>
+  <si>
+    <t>紫苑「……怖いなら、怖いって言っていいんだよ」</t>
+  </si>
+  <si>
+    <t>ノア「……怖い、というのは、正確な表現じゃ……」</t>
+  </si>
+  <si>
+    <t>言葉が、そこで途切れた。強張っていた顔が、じわりと崩れていく。</t>
+  </si>
+  <si>
+    <t>ノア「……ずっと、考えて……それでも、追いつかなくて……」</t>
+  </si>
+  <si>
+    <t>立ち上がろうとした足が、瓦礫に取られてよろめく。</t>
+  </si>
+  <si>
+    <t>紫苑は咄嗟に、倒れかけたその体を抱きとめた。</t>
+  </si>
+  <si>
+    <t>腕の中は、驚くほど軽く、冷え切って、小さく震えていた。</t>
+  </si>
+  <si>
+    <t>紫苑はその体を、少し強く抱き寄せる。</t>
+  </si>
+  <si>
+    <t>紫苑「……怖かったんだね」</t>
+  </si>
+  <si>
+    <t>ノア「……っ……」</t>
+  </si>
+  <si>
+    <t>堪えていたものが、そこで決壊した。ノアは紫苑にしがみつき、声を上げて泣き始める。</t>
+  </si>
+  <si>
+    <t>紫苑は何も言わず、ただその背中を撫で続けた。</t>
+  </si>
+  <si>
+    <t>やがて、嗚咽が少しずつ収まっていく。</t>
+  </si>
+  <si>
+    <t>紫苑「……一緒に、友達を探そう」</t>
+  </si>
+  <si>
+    <t>ノア「……うん」</t>
+  </si>
+  <si>
+    <t>木々に覆われた廃墟の中、紫苑は微かな気配を感じ取った。呼吸の音。人間のものだ。</t>
+    <rPh sb="0" eb="2">
+      <t>キギ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハイキョ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナカ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2212,7 +2237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB1720EA-3884-4C74-9D88-634359EF668C}">
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -2222,32 +2247,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>323</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
@@ -2262,52 +2287,42 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
         <v>335</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
@@ -2315,14 +2330,89 @@
         <v>336</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>338</v>
-      </c>
-    </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>332</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
